--- a/LubanTmpl/Datas/ui_param.xlsx
+++ b/LubanTmpl/Datas/ui_param.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30319"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Thirds\XIHFrameWork\LubanTmpl\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9AACFF-6D14-46F6-824D-2F4B96FABF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF4BD9E-413F-4EE4-AE21-7D6ACDEBA169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29400" yWindow="660" windowWidth="28830" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1215" yWindow="1350" windowWidth="28830" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -41,31 +41,31 @@
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>dialog_name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>界面类名</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>package_name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>component_name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>c</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>layer</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>isFull</t>
@@ -75,46 +75,46 @@
   </si>
   <si>
     <t>包名</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>组件名</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>层级</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>是否全屏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>是否背景模糊</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SceneChangeDialog</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SceneChange</t>
   </si>
   <si>
     <t>TopMost</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>dependency_packages</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>依赖的其他包名</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>list,string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SystemTipDialog</t>
@@ -132,46 +132,68 @@
     <t>ChooseDialog</t>
   </si>
   <si>
+    <t>Popup</t>
+  </si>
+  <si>
+    <t>HomeDialog</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>useBatch</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否批处理</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mode</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>WaitMask</t>
+  </si>
+  <si>
+    <t>BattleSettingDialog</t>
+  </si>
+  <si>
+    <t>Setup</t>
+  </si>
+  <si>
+    <t>Setting</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>Choose</t>
-  </si>
-  <si>
-    <t>Popup</t>
-  </si>
-  <si>
-    <t>HomeDialog</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Stack</t>
-  </si>
-  <si>
-    <t>useBatch</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否批处理</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mode</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -259,33 +281,52 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
     <cellStyle name="差" xfId="1" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="4" xr:uid="{D51640B6-43B1-4EC8-B106-2D267421C9BF}"/>
+    <cellStyle name="常规 3" xfId="3" xr:uid="{A0144ECF-6254-4F91-9534-227C2F76E6AA}"/>
     <cellStyle name="好" xfId="2" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -559,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB8"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -597,7 +638,7 @@
         <v>14</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J1"/>
       <c r="K1"/>
@@ -636,7 +677,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>3</v>
@@ -645,7 +686,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -741,7 +782,7 @@
         <v>19</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -816,11 +857,11 @@
       <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
         <v>31</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -834,16 +875,16 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
         <v>33</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" t="s">
         <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -855,8 +896,62 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A9" s="9"/>
+      <c r="B9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10"/>
+      <c r="L9" s="9"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A10" s="15"/>
+      <c r="B10" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="13"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
